--- a/Common Utils/data.xlsx
+++ b/Common Utils/data.xlsx
@@ -9,11 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7350" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7350" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="usermanagement" sheetId="2" r:id="rId2"/>
+    <sheet name="postmandata" sheetId="3" r:id="rId3"/>
+    <sheet name="Reports" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>Location</t>
   </si>
@@ -103,13 +105,64 @@
   </si>
   <si>
     <t>ConfirmPassword</t>
+  </si>
+  <si>
+    <t>deviceId</t>
+  </si>
+  <si>
+    <t>tms</t>
+  </si>
+  <si>
+    <t>temp</t>
+  </si>
+  <si>
+    <t>humidity</t>
+  </si>
+  <si>
+    <t>WTH_0000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensor Function </t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Sensor Readings</t>
+  </si>
+  <si>
+    <t>WTH50</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> startDay</t>
+  </si>
+  <si>
+    <t>startMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> startYear</t>
+  </si>
+  <si>
+    <t> endDay</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> endMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> endYear</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +188,20 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -157,11 +224,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -604,4 +680,142 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1744606424</v>
+      </c>
+      <c r="C2" s="4">
+        <v>37</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
+    <col min="4" max="4" width="30.85546875" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2025</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2025</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Common Utils/data.xlsx
+++ b/Common Utils/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
   <si>
     <t xml:space="preserve">Region </t>
   </si>
@@ -191,6 +191,36 @@
   </si>
   <si>
     <t>Warning</t>
+  </si>
+  <si>
+    <t>RoleName</t>
+  </si>
+  <si>
+    <t>RoleTag</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>SUPER_ADMIN</t>
+  </si>
+  <si>
+    <t>my Test</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Mamatha</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>dashboard</t>
+  </si>
+  <si>
+    <t>Role015494</t>
   </si>
 </sst>
 </file>
@@ -713,7 +743,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="6" bestFit="1" customWidth="1"/>
@@ -725,9 +755,13 @@
     <col min="7" max="7" width="27.140625" style="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26" style="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -755,8 +789,23 @@
       <c r="I1" s="15" t="s">
         <v>29</v>
       </c>
+      <c r="J1" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
@@ -770,7 +819,7 @@
         <v>33</v>
       </c>
       <c r="E2" s="5">
-        <v>9963060311</v>
+        <v>9963060211</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -783,6 +832,21 @@
       </c>
       <c r="I2" s="17" t="s">
         <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
